--- a/customer_service_forms/031_infant_intake_form--customer_service_forms.xlsx
+++ b/customer_service_forms/031_infant_intake_form--customer_service_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1279,17 +1279,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>infant_intake_form_language_choices</t>
+          <t>infant_intake_form_is_pregnant_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1301,29 +1301,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>infant_intake_form_is_pregnant_choices</t>
+          <t>infant_intake_form_pregnancy_status_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>singleton</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Singleton</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>singleton</t>
+          <t>twins</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Singleton</t>
+          <t>Twins</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>twins</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Twins</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1369,29 +1369,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>multiple_birth</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Multiple birth</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>infant_intake_form_pregnancy_status_choices</t>
+          <t>infant_intake_form_first_language_learned_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>multiple_birth</t>
+          <t>infant_mom</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Multiple birth</t>
+          <t>Infant Mom</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>infant_mom</t>
+          <t>infant_dad</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Infant Mom</t>
+          <t>Infant Dad</t>
         </is>
       </c>
     </row>
@@ -1420,29 +1420,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>infant_dad</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Infant Dad</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>infant_intake_form_first_language_learned_choices</t>
+          <t>infant_intake_form_language_preference_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>english</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>spanish</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spanish</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>french</t>
+          <t>german</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>French</t>
+          <t>German</t>
         </is>
       </c>
     </row>
@@ -1522,27 +1522,10 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>german</t>
+          <t>arabic</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
-        <is>
-          <t>German</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>infant_intake_form_language_preference_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>arabic</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
         <is>
           <t>Arabic</t>
         </is>
